--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5406.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5406.xlsx
@@ -2263,6 +2263,9 @@
       <c r="C35" t="n">
         <v>3</v>
       </c>
+      <c r="D35" t="n">
+        <v>2.2</v>
+      </c>
       <c r="E35" t="n">
         <v>2.875</v>
       </c>
@@ -2276,17 +2279,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C2HEX@HEX, L2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C2HEX@HEX, L2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5406-40-32 (PARTcommunity / CADENAS, C2HEX@HEX=C, L2@DRIVE=L, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5406-40-32 (PARTcommunity / CADENAS, C2HEX@HEX=C, L2@DRIVE=L, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
